--- a/aspnet-core/src/ProjectManagement.Web.Host/wwwroot/template/Invoice.xlsx
+++ b/aspnet-core/src/ProjectManagement.Web.Host/wwwroot/template/Invoice.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ncc-erp-project\aspnet-core\src\ProjectManagement.Web.Host\wwwroot\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP_HN2\ncc-erp-project\aspnet-core\src\ProjectManagement.Web.Host\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33E33FD-1DF6-40E1-8CC8-9A37234D42B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -32,7 +33,7 @@
     <definedName name="PaymentDueBy" localSheetId="0">Invoice!$B$4</definedName>
     <definedName name="TransferFee" localSheetId="0">Invoice!$G$18</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -42,15 +43,6 @@
     <t>INVOICE</t>
   </si>
   <si>
-    <t>NCCPLUS VIET NAM JOINT STOCK COMPANY</t>
-  </si>
-  <si>
-    <t>No 3B Lane 69, Nguyen Phuc Lai Street</t>
-  </si>
-  <si>
-    <t>O Cho Dua Precinct, Dong Da District</t>
-  </si>
-  <si>
     <t>Ha Noi, Viet Nam</t>
   </si>
   <si>
@@ -106,12 +98,21 @@
   </si>
   <si>
     <t>NOTE</t>
+  </si>
+  <si>
+    <t>Lot No. 210, 2nd Floor, CT3 Building, The Pride</t>
+  </si>
+  <si>
+    <t>An Hung New Urban Area, Ha Dong Ward</t>
+  </si>
+  <si>
+    <t>NCCPLUS JSC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd\ mmmm\ yyyy"/>
@@ -337,195 +338,171 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -772,7 +749,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Billing Invoice" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Billing Invoice" pivot="0" count="4">
+    <tableStyle name="Billing Invoice" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -805,26 +782,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="InvoiceDetails" displayName="InvoiceDetails" ref="B14:G15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InvoiceDetails" displayName="InvoiceDetails" ref="B14:G15">
   <tableColumns count="6">
-    <tableColumn id="1" name="NAME" dataDxfId="9"/>
-    <tableColumn id="6" name="PROJECT" dataDxfId="8"/>
-    <tableColumn id="5" name="RATE" dataDxfId="7"/>
-    <tableColumn id="2" name="RATE TYPE" dataDxfId="6"/>
-    <tableColumn id="3" name="WORKING TIME" dataDxfId="5"/>
-    <tableColumn id="4" name="LINE TOTAL" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="NAME" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PROJECT" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="RATE" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="RATE TYPE" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="WORKING TIME" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="LINE TOTAL" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="Billing Invoice" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InvoiceDetails4" displayName="InvoiceDetails4" ref="B3:E4" insertRow="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="InvoiceDetails4" displayName="InvoiceDetails4" ref="B3:E4" insertRow="1">
   <tableColumns count="4">
-    <tableColumn id="1" name="DATE AT" dataDxfId="3"/>
-    <tableColumn id="6" name="MAN DAY" dataDxfId="2"/>
-    <tableColumn id="5" name="TASK NAME" dataDxfId="1"/>
-    <tableColumn id="2" name="NOTE" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="DATE AT" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MAN DAY" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="TASK NAME" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NOTE" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Billing Invoice" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1056,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
     <pageSetUpPr autoPageBreaks="0"/>
@@ -1080,213 +1057,213 @@
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="43"/>
+      <c r="C2" s="35"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="2:7" ht="24" customHeight="1" thickTop="1">
-      <c r="B3" s="55">
+      <c r="B3" s="49">
         <v>44015</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="41"/>
     </row>
     <row r="4" spans="2:7" ht="24" customHeight="1">
       <c r="B4" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="50"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="2:7" ht="12.75" customHeight="1">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="8"/>
-      <c r="G10" s="10"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="2:7" ht="6.75" customHeight="1">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="8"/>
-      <c r="G11" s="10"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="2:7" ht="6" customHeight="1" thickBot="1">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="2:7" ht="15" thickTop="1">
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="2:7" ht="15">
       <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="18.75" customHeight="1">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+    </row>
+    <row r="16" spans="2:7" ht="18" customHeight="1">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="18.75" customHeight="1">
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-    </row>
-    <row r="16" spans="2:7" ht="18" customHeight="1">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="45">
+      <c r="G16" s="37">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="18" customHeight="1">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="45">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="37">
         <f>0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:8" s="33" customFormat="1" ht="18" customHeight="1">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="45">
+    <row r="18" spans="2:8" ht="18" customHeight="1">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="61"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="2:8" ht="18" customHeight="1" thickBot="1">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="62"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="21" spans="2:8" ht="15" thickTop="1"/>
     <row r="22" spans="2:8" ht="15">
-      <c r="B22" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="26"/>
+      <c r="B22" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="2:8" ht="15">
-      <c r="B23" s="28"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="2:8" ht="27" customHeight="1">
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="27"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="26"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -1314,60 +1291,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:F6"/>
   <sheetFormatPr defaultRowHeight="10.5"/>
   <cols>
-    <col min="1" max="1" width="4" style="31" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="42" customWidth="1"/>
-    <col min="4" max="4" width="20" style="31" customWidth="1"/>
-    <col min="5" max="5" width="52.42578125" style="31" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="31"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" style="34" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="27">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="2:6" ht="15">
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-    </row>
-    <row r="3" spans="2:6" s="35" customFormat="1" ht="15">
-      <c r="B3" s="32" t="s">
+      <c r="E3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="33"/>
-    </row>
-    <row r="4" spans="2:6" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="33"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="2:6" ht="18" customHeight="1">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="2:6" ht="11.25" thickBot="1">
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-    </row>
-    <row r="6" spans="2:6" ht="11.25" thickTop="1">
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-    </row>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+    </row>
+    <row r="6" spans="2:6" ht="11.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:E2"/>
